--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0022.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0022.xlsx
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Những dự đoán tiên tiến, bao gồm cả &lt;te href=750035&gt;Etheric Sea&lt;/te&gt; và các Tổ Tacet, vẫn nằm ngoài tầm với của chúng ta.</t>
+          <t>Những dự đoán tiên tiến, bao gồm cả &lt;te href=750035&gt;Biển Ether&lt;/te&gt; và các Tổ Tacet, vẫn nằm ngoài tầm với của chúng ta.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Nhưng... giờ không phải lúc ngắm cảnh đâu! Mau cứu ta đi!</t>
+          <t>Nhưng... giờ không phải lúc ngắm cảnh đâu! Mau cứu tao đi!</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Cậu là con vẹt à?</t>
+          <t>Mày là con vẹt à?</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Chờ đã... {Male=Hắn;Female=Cô ấy} chết rồi hay chỉ bất tỉnh thôi?</t>
+          <t>Chờ đã... {Male=he;Female=she} chết rồi hay chỉ bất tỉnh thôi?</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Ta có vài phụ tùng và dầu thừa đây. Cậu lấy hết đi!</t>
+          <t>Tao có vài phụ tùng và dầu thừa đây. Cậu lấy hết đi!</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Cậu có thể thử tạo Điểm Móc với thiết bị gần đó để lên được bệ. Đó chính là cái mà ta gọi là "Chiến Thuật Trên Không"!</t>
+          <t>Cậu có thể thử tạo Điểm Móc với thiết bị gần đó để lên được bệ. Đó chính là cái mà tao gọi là "Chiến Thuật Trên Không"!</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Lần trước Encore đến Kim Châu, mọi người bận rộn quá nên chẳng kịp chơi cùng nhau.</t>
+          <t>Lần trước Encore đến Jinzhou, mọi người bận rộn quá nên chẳng kịp chơi cùng nhau.</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Đợi đến khi ngươi nghe câu chuyện thật đi. Ta chưa muốn tiết lộ gì đâu!</t>
+          <t>Đợi đến khi mày nghe câu chuyện thật đi. Tao chưa muốn tiết lộ gì đâu!</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Nếu cậu thích nghe chuyện, Rover à, biết đâu cậu còn được bước vào một câu chuyện đấy. Cậu thấy thế nào, các bé cừu?</t>
+          <t>Nếu cậu thích nghe chuyện, Vận Mệnh Giả à, biết đâu cậu còn được bước vào một câu chuyện đấy. Cậu thấy thế nào, các bé cừu?</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Ta còn việc phải làm.</t>
+          <t>Tao còn việc phải làm.</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Những trận đấu đó hơi... quá thật với ta.</t>
+          <t>Những trận đấu đó hơi... quá thật với tao.</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Chắc chắn là được. Ngươi thấy chúng đánh nhau với lũ quái đó chưa? Vài món đồ cổ chẳng là gì cả!</t>
+          <t>Chắc chắn là được. Mày thấy chúng đánh nhau với lũ quái đó chưa? Vài món đồ cổ chẳng là gì cả!</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Ê! Ta nghe thấy rồi đấy!</t>
+          <t>Ê! Tao nghe thấy rồi đấy!</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Cậu thấy câu chuyện của Encore thế nào, {Male=anh;Female=chị}? Hay tuyệt vời luôn ấy!</t>
+          <t>Cậu thấy câu chuyện của Encore thế nào, {Male=mister;Female=miss}? Hay tuyệt vời luôn ấy!</t>
         </is>
       </c>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Ê! Ta thấy cậu đứng một mình ở đây. Tên cậu là gì?</t>
+          <t>Ê! Tao thấy cậu đứng một mình ở đây. Tên cậu là gì?</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Doanh! Hiểu rồi! Đây là {PlayerName}, {Male=anh ấy;Female=cô ấy} là đội trưởng Đội Cừu Nhung đấy!</t>
+          <t>Doanh! Hiểu rồi! Đây là {PlayerName}, {Male=he;Female=she} là đội trưởng Đội Cừu Nhung đấy!</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Vâng. Xin chào. Cậu đến để hỏi về suy nghĩ của tôi về câu chuyện phải không? Thực ra tôi cũng có điều muốn hỏi cậu...</t>
+          <t>Vâng. Xin chào. bạn đến để hỏi về suy nghĩ của tôi về câu chuyện phải không? Thực ra tôi cũng có điều muốn hỏi bạn...</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Ta kể với bố về tấm bản đồ, ông chỉ ôm ta mà không nói gì cả.</t>
+          <t>Tao kể với bố về tấm bản đồ, ông chỉ ôm tao mà không nói gì cả.</t>
         </is>
       </c>
     </row>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Đợi đến khi ngươi thấy tụi ta còn làm được gì nữa! Đúng không, {PlayerName}?</t>
+          <t>Đợi đến khi mày thấy tụi tao còn làm được gì nữa! Đúng không, {PlayerName}?</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Lần đầu ta nhìn thấy thanh kiếm đó, ta có cảm giác như đây có thể là một trò chơi mà mẹ để lại cho ta.</t>
+          <t>Lần đầu tao nhìn thấy thanh kiếm đó, tao có cảm giác như đây có thể là một trò chơi mà mẹ để lại cho tao.</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Ta cũng không. Ngay cả Ying vừa hỏi ta cái khiên đó có thật không. Cậu nghĩ sao?</t>
+          <t>Tao cũng không. Ngay cả Ying vừa hỏi tao cái khiên đó có thật không. Cậu nghĩ sao?</t>
         </is>
       </c>
     </row>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Tuyệt lắm! Ta biết phải gọi ai nếu cần tìm thứ gì đó rồi. Ta đi gọi Ying đây!</t>
+          <t>Tuyệt lắm! Tao biết phải gọi ai nếu cần tìm thứ gì đó rồi. Tao đi gọi Ying đây!</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Giờ ta mới thấy, khiên và kiếm này chính là những bảo vật mà mẹ đã để lại cho ta.</t>
+          <t>Giờ tao mới thấy, khiên và kiếm này chính là những bảo vật mà mẹ đã để lại cho tao.</t>
         </is>
       </c>
     </row>
